--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44883</v>
+        <v>45463</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45300</v>
+        <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45463</v>
+        <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE8"/>
+  <dimension ref="A1:AE9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 34310-2024</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,14 +704,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45524</v>
+        <v>45300</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -777,14 +777,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45463</v>
+        <v>45300</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -840,7 +840,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 45983-2023</t>
+          <t>A 34310-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45196</v>
+        <v>45524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -930,7 +930,7 @@
         <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 45983-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -996,14 +996,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45300</v>
+        <v>45196</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1056,10 +1056,10 @@
       </c>
       <c r="V7" s="2" t="inlineStr"/>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,65 +1069,138 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45300</v>
+        <v>45463</v>
       </c>
       <c r="E8" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SKURUP</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 38010-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>46280</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="E9" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>SKÅNE LÄN</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>SKURUP</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 34310-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,14 +704,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45300</v>
+        <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -777,14 +777,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45300</v>
+        <v>45463</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -840,7 +840,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 34310-2024</t>
+          <t>A 45983-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45524</v>
+        <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -930,7 +930,7 @@
         <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 45983-2023</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -996,14 +996,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45196</v>
+        <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45463</v>
+        <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45463</v>
+        <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44883</v>
+        <v>45300</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45300</v>
+        <v>46280</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46280</v>
+        <v>45463</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44883</v>
+        <v>45463</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45300</v>
+        <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46280</v>
+        <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45463</v>
+        <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>45463</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>45463</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 34310-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45524</v>
+        <v>44883</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 34310-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45463</v>
+        <v>45524</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44883</v>
+        <v>45300</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45300</v>
+        <v>45463</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 34310-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44883</v>
+        <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 34310-2024</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45524</v>
+        <v>45463</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45300</v>
+        <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45463</v>
+        <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45463</v>
+        <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44883</v>
+        <v>45300</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45300</v>
+        <v>46280</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46280</v>
+        <v>45463</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45300</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>46280</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45463</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45300</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>46280</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45463</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44883</v>
+        <v>45463</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45300</v>
+        <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46280</v>
+        <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45463</v>
+        <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45463</v>
+        <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44883</v>
+        <v>45300</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45300</v>
+        <v>46280</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46280</v>
+        <v>45463</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 34310-2024</t>
+          <t>A 45983-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45524</v>
+        <v>45196</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -784,7 +784,7 @@
         <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 45983-2023</t>
+          <t>A 34310-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45196</v>
+        <v>45524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45300</v>
+        <v>45463</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46280</v>
+        <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45463</v>
+        <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 45983-2023</t>
+          <t>A 34310-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45196</v>
+        <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -784,7 +784,7 @@
         <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 34310-2024</t>
+          <t>A 45983-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45524</v>
+        <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45463</v>
+        <v>45300</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45300</v>
+        <v>46280</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46280</v>
+        <v>45463</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44883</v>
+        <v>45463</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45300</v>
+        <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -996,14 +996,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45300</v>
+        <v>46280</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46280</v>
+        <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>0.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1142,14 +1142,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45463</v>
+        <v>45300</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>45463</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>46280</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45300</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>45463</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>46280</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45300</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45463</v>
+        <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44883</v>
+        <v>45300</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -996,14 +996,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46280</v>
+        <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45300</v>
+        <v>46280</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.8</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1142,14 +1142,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45300</v>
+        <v>45463</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44883</v>
+        <v>45463</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45300</v>
+        <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -996,14 +996,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45300</v>
+        <v>46280</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46280</v>
+        <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>0.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1142,14 +1142,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45463</v>
+        <v>45300</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 34310-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45524</v>
+        <v>44883</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -784,7 +784,7 @@
         <v>45463</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 45983-2023</t>
+          <t>A 34310-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45196</v>
+        <v>45524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 45983-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44883</v>
+        <v>45196</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -996,14 +996,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46280</v>
+        <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1076,7 +1076,7 @@
         <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1142,14 +1142,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45300</v>
+        <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 34310-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44883</v>
+        <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -784,7 +784,7 @@
         <v>45463</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 34310-2024</t>
+          <t>A 45983-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45524</v>
+        <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 45983-2023</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45196</v>
+        <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.6</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 34310-2024</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45524</v>
+        <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 34310-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45463</v>
+        <v>45524</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44883</v>
+        <v>45300</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45300</v>
+        <v>44883</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>45524</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45300</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>44883</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>45524</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>45300</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>44883</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45463</v>
+        <v>46280</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.3</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -784,7 +784,7 @@
         <v>45524</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 45983-2023</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45196</v>
+        <v>45463</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 45983-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45300</v>
+        <v>45196</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -996,14 +996,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45300</v>
+        <v>44883</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44883</v>
+        <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1142,14 +1142,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46280</v>
+        <v>45300</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 34310-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46280</v>
+        <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 34310-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45524</v>
+        <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -840,7 +840,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 45983-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45463</v>
+        <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 45983-2023</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45196</v>
+        <v>45300</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -996,14 +996,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44883</v>
+        <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45300</v>
+        <v>46280</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.8</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1142,14 +1142,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45300</v>
+        <v>45463</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 34310-2024</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45524</v>
+        <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 34310-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44883</v>
+        <v>45524</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45300</v>
+        <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46280</v>
+        <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45463</v>
+        <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45463</v>
+        <v>44883</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -784,7 +784,7 @@
         <v>45524</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44883</v>
+        <v>45300</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45300</v>
+        <v>46280</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46280</v>
+        <v>45463</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 34310-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44883</v>
+        <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 34310-2024</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45524</v>
+        <v>45463</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45300</v>
+        <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46280</v>
+        <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45463</v>
+        <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>45463</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>45463</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45463</v>
+        <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44883</v>
+        <v>45300</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1003,7 +1003,7 @@
         <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45300</v>
+        <v>46280</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46280</v>
+        <v>45463</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44883</v>
+        <v>45463</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45300</v>
+        <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -996,14 +996,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45300</v>
+        <v>46280</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46280</v>
+        <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>0.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1142,14 +1142,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45463</v>
+        <v>45300</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45463</v>
+        <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44883</v>
+        <v>45300</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -996,14 +996,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46280</v>
+        <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45300</v>
+        <v>46280</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.8</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1142,14 +1142,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45300</v>
+        <v>45463</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 34310-2024</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,14 +704,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45524</v>
+        <v>45300</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -777,14 +777,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44883</v>
+        <v>45300</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -840,7 +840,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 45983-2023</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45196</v>
+        <v>46280</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>9</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 34310-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45300</v>
+        <v>45524</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -996,14 +996,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45300</v>
+        <v>45463</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 45983-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46280</v>
+        <v>45196</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>0.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45463</v>
+        <v>44883</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,14 +704,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45300</v>
+        <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -777,14 +777,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45300</v>
+        <v>46280</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -840,7 +840,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 34310-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46280</v>
+        <v>45524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 34310-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45524</v>
+        <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 45983-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1000,10 +1000,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45463</v>
+        <v>45196</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 45983-2023</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45196</v>
+        <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1142,14 +1142,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44883</v>
+        <v>45300</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46280</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45196</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45300</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>45463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>46280</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45196</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45300</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 34310-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45463</v>
+        <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46280</v>
+        <v>45463</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -840,7 +840,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 34310-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45524</v>
+        <v>46280</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 45983-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44883</v>
+        <v>45196</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 45983-2023</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1000,10 +1000,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45196</v>
+        <v>44883</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.6</v>
+        <v>5.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45300</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 34310-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45524</v>
+        <v>44883</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -784,7 +784,7 @@
         <v>45463</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 34310-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46280</v>
+        <v>45524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -930,7 +930,7 @@
         <v>45196</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1000,10 +1000,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44883</v>
+        <v>46280</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45300</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 45983-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44883</v>
+        <v>45196</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45463</v>
+        <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -840,7 +840,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 34310-2024</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -850,14 +850,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45524</v>
+        <v>45300</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 45983-2023</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45196</v>
+        <v>45300</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 38010-2026</t>
+          <t>A 34310-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1000,10 +1000,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46280</v>
+        <v>45524</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45300</v>
+        <v>45463</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 38010-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1142,14 +1142,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45300</v>
+        <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>

--- a/Översikt SKURUP.xlsx
+++ b/Översikt SKURUP.xlsx
@@ -601,7 +601,7 @@
         <v>45607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 45983-2023</t>
+          <t>A 34310-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45196</v>
+        <v>45524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 54782-2022</t>
+          <t>A 25617-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44883</v>
+        <v>45463</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -840,7 +840,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 843-2024</t>
+          <t>A 45983-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -850,14 +850,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45300</v>
+        <v>45196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 844-2024</t>
+          <t>A 54782-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45300</v>
+        <v>44883</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 34310-2024</t>
+          <t>A 843-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -996,14 +996,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45524</v>
+        <v>45300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25617-2024</t>
+          <t>A 844-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45463</v>
+        <v>45300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
